--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bounty Hunters</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1017.2412711985547</v>
+        <v>1027.7153682632659</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-09-08T12:46:09.197Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Spirit</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
         <v>4</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
       <c r="E24">
-        <v>1016.7402640066111</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Spirit</v>
       </c>
       <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>3</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
       <c r="E25">
-        <v>1015.0604120732232</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J25" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K25" t="str">
         <v>none</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-23T07:39:14.984Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Huns</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1015</v>
+        <v>1015.2960629803374</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-09-08T12:45:52.294Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Onyx Ravens</v>
+        <v>Enemy</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>1014.9877256835035</v>
+        <v>1015.2835913684207</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J27" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K27" t="str">
         <v>none</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-09-08T12:44:38.294Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>1014.7261395369545</v>
+        <v>1015.2830286307026</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-08-23T07:38:19.410Z</v>
+        <v>2026-09-08T12:45:02.441Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BIG Academy</v>
+        <v>Imperial</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>1014.7261395369545</v>
+        <v>1015.2830286307026</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J29" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K29" t="str">
         <v>none</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-08-23T07:38:11.231Z</v>
+        <v>2026-09-08T12:45:59.510Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SKYFURY</v>
+        <v>BC.Game</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>1014.7261395369545</v>
+        <v>1015.251783966838</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-08-23T07:38:02.605Z</v>
+        <v>2026-09-08T12:45:14.013Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENCE Academy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>2</v>
       </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
       <c r="E31">
-        <v>1014.7261395369545</v>
+        <v>1015.0604120732232</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-23T07:37:55.979Z</v>
+        <v>2026-08-23T07:39:14.984Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Counter Logic</v>
+        <v>Astralis</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>1014.6510123894305</v>
+        <v>1015.0130343496347</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J32" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K32" t="str">
         <v>none</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-07-07T04:08:50.601Z</v>
+        <v>2026-09-08T12:44:53.425Z</v>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TYLOO</v>
+        <v>The Huns</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>1014.128742285643</v>
+        <v>1015</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J33" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K33" t="str">
         <v>none</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N33" t="str">
         <v/>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lux Tenebris</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>1013.6802515527833</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J34" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K34" t="str">
         <v>none</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-09-06T03:52:40.291Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N34" t="str">
         <v/>
@@ -2203,19 +2203,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OG</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>1013.5266895185538</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-08-23T07:38:19.410Z</v>
       </c>
       <c r="N35" t="str">
         <v/>
@@ -2256,19 +2256,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BESTIA</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>1005.0046329623956</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J36" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K36" t="str">
         <v>none</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-08-23T07:38:11.231Z</v>
       </c>
       <c r="N36" t="str">
         <v/>
@@ -2309,19 +2309,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>G2</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>1002.6421965170028</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-08-23T07:38:02.605Z</v>
       </c>
       <c r="N37" t="str">
         <v/>
@@ -2362,19 +2362,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>hoorai</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>1000.4888979238718</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v>2026-08-23T07:37:55.979Z</v>
       </c>
       <c r="N38" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Take Flyte</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>1000.3086743488057</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-07-23T22:14:26.816Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N39" t="str">
         <v/>
@@ -2468,19 +2468,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Avangar</v>
+        <v>TYLOO</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>1000</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N40" t="str">
         <v/>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bravado</v>
+        <v>OG</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1000</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J41" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K41" t="str">
         <v>none</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N41" t="str">
         <v/>
@@ -2574,19 +2574,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FORZE</v>
+        <v>BESTIA</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42">
-        <v>1000</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J42" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K42" t="str">
         <v>none</v>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N42" t="str">
         <v/>
@@ -2627,19 +2627,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>GATERON</v>
+        <v>G2</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>1000</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J43" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K43" t="str">
         <v>none</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N43" t="str">
         <v/>
@@ -2680,19 +2680,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Hesta</v>
+        <v>MOUZ</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>1000</v>
+        <v>1001.5100345642078</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>2026-09-08T12:44:45.656Z</v>
       </c>
       <c r="N44" t="str">
         <v/>
@@ -2733,19 +2733,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kONO</v>
+        <v>hoorai</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -2786,19 +2786,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>LGB</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1000</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Rogue</v>
+        <v>Avangar</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Shika</v>
+        <v>Bravado</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tsunami</v>
+        <v>FORZE</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>BC.Game</v>
+        <v>GATERON</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>1000</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-09-06T03:30:01.464Z</v>
+        <v/>
       </c>
       <c r="N50" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>3DMAX</v>
+        <v>Hesta</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>1000</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="str">
-        <v>2026-09-06T03:33:30.718Z</v>
+        <v/>
       </c>
       <c r="N51" t="str">
         <v/>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Imperial</v>
+        <v>kONO</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>1000</v>
@@ -3131,7 +3131,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J52" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K52" t="str">
         <v>none</v>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="str">
-        <v>2026-09-06T03:36:02.430Z</v>
+        <v/>
       </c>
       <c r="N52" t="str">
         <v/>
@@ -3157,16 +3157,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Envy</v>
+        <v>LGB</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>1000</v>
@@ -3184,7 +3184,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J53" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K53" t="str">
         <v>none</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="str">
-        <v>2026-09-06T03:39:57.123Z</v>
+        <v/>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -3210,16 +3210,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Enemy</v>
+        <v>Rogue</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>1000</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="str">
-        <v>2026-09-06T03:42:24.700Z</v>
+        <v/>
       </c>
       <c r="N54" t="str">
         <v/>
@@ -3263,16 +3263,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ARCRED</v>
+        <v>Shika</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>1000</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="str">
-        <v>2026-09-06T03:42:44.811Z</v>
+        <v/>
       </c>
       <c r="N55" t="str">
         <v/>
@@ -3316,16 +3316,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Lynn Vision</v>
+        <v>Tsunami</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>1000</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="str">
-        <v>2026-09-06T03:43:07.819Z</v>
+        <v/>
       </c>
       <c r="N56" t="str">
         <v/>
@@ -3369,19 +3369,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FlyQuest</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="str">
-        <v>2026-09-06T03:55:39.980Z</v>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N57" t="str">
         <v/>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Spirit Academy</v>
+        <v>True Rippers</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -3449,7 +3449,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J58" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K58" t="str">
         <v>none</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N58" t="str">
         <v/>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>True Rippers</v>
+        <v>FaZe</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N59" t="str">
         <v/>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>FaZe</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N60" t="str">
         <v/>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>iBUYPOWER</v>
+        <v>GODSENT</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -3608,7 +3608,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J61" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K61" t="str">
         <v>none</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N61" t="str">
         <v/>
@@ -3634,19 +3634,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>GODSENT</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>999.7251809772306</v>
+        <v>999.7039370196626</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J62" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K62" t="str">
         <v>none</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-08-08T06:10:52.072Z</v>
       </c>
       <c r="N62" t="str">
         <v/>
@@ -3687,19 +3687,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Underground</v>
+        <v>Kinguin</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>999.7167190829146</v>
+        <v>999.7039370196626</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="str">
-        <v>2026-09-06T03:51:19.596Z</v>
+        <v>2026-08-08T06:06:19.166Z</v>
       </c>
       <c r="N63" t="str">
         <v/>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>MAD Lions</v>
+        <v>Gambit</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="str">
-        <v>2026-08-08T06:10:52.072Z</v>
+        <v>2026-08-08T06:06:03.563Z</v>
       </c>
       <c r="N64" t="str">
         <v/>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Kinguin</v>
+        <v>VeryGames</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="str">
-        <v>2026-08-08T06:06:19.166Z</v>
+        <v>2026-08-08T06:05:55.763Z</v>
       </c>
       <c r="N65" t="str">
         <v/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Gambit</v>
+        <v>Misfits</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="str">
-        <v>2026-08-08T06:06:03.563Z</v>
+        <v>2026-08-08T06:04:44.394Z</v>
       </c>
       <c r="N66" t="str">
         <v/>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>VeryGames</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="str">
-        <v>2026-08-08T06:05:55.763Z</v>
+        <v>2026-08-08T06:04:29.697Z</v>
       </c>
       <c r="N67" t="str">
         <v/>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Misfits</v>
+        <v>mousesports</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -3979,7 +3979,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J68" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K68" t="str">
         <v>none</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="str">
-        <v>2026-08-08T06:04:44.394Z</v>
+        <v>2026-08-08T06:04:14.871Z</v>
       </c>
       <c r="N68" t="str">
         <v/>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Space Soldiers</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="str">
-        <v>2026-08-08T06:04:29.697Z</v>
+        <v>2026-08-08T06:03:54.346Z</v>
       </c>
       <c r="N69" t="str">
         <v/>
@@ -4058,19 +4058,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>mousesports</v>
+        <v>M80</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>999.7039370196626</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J70" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K70" t="str">
         <v>none</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="str">
-        <v>2026-08-08T06:04:14.871Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N70" t="str">
         <v/>
@@ -4111,19 +4111,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Movistar KOI</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>999.7039370196626</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J71" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K71" t="str">
         <v>none</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="str">
-        <v>2026-08-08T06:03:54.346Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N71" t="str">
         <v/>
@@ -4164,19 +4164,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ECSTATIC</v>
+        <v>Orbit</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>999.7039370196626</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="str">
-        <v>2026-09-06T03:51:37.526Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N72" t="str">
         <v/>
@@ -4217,19 +4217,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Aravt</v>
+        <v>Alliance</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>2</v>
       </c>
       <c r="E73">
-        <v>999.7039370196626</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J73" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K73" t="str">
         <v>none</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="str">
-        <v>2026-09-06T03:51:47.647Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N73" t="str">
         <v/>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Astralis</v>
+        <v>Homyno</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>2</v>
       </c>
       <c r="E74">
-        <v>999.7039370196626</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J74" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K74" t="str">
         <v>none</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="str">
-        <v>2026-09-06T03:52:06.720Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>M80</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4335,7 +4335,7 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>999.672340544519</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N75" t="str">
         <v/>
@@ -4376,19 +4376,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Solid</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>999.4408194717619</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,19 +4429,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Orbit</v>
+        <v>ENCE</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alliance</v>
+        <v>Nexus</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Homyno</v>
+        <v>MIBR</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MenaceGG</v>
+        <v>Wizards</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4600,7 +4600,7 @@
         <v>2</v>
       </c>
       <c r="E80">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Solid</v>
+        <v>RED Canids</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>999.4088515186523</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ENCE</v>
+        <v>Rebels</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E82">
-        <v>999.4088515186523</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nexus</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4759,7 +4759,7 @@
         <v>2</v>
       </c>
       <c r="E83">
-        <v>999.4088515186523</v>
+        <v>996.0904918173039</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-07-23T22:12:51.919Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>MIBR</v>
+        <v>Mythic</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -4809,10 +4809,10 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84">
-        <v>999.4088515186523</v>
+        <v>986.2948766874508</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-07-23T22:00:15.992Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,19 +4853,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Wizards</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>999.4062521695108</v>
+        <v>985</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J85" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K85" t="str">
         <v>none</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-07-30T05:44:28.360Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,19 +4906,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>RED Canids</v>
+        <v>HAVU</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>999.3397745397444</v>
+        <v>985</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4933,7 +4933,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J86" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K86" t="str">
         <v>none</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-07-30T05:44:22.588Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,19 +4959,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Rebels</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B87">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>999.3232682842747</v>
+        <v>985</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-30T05:44:15.749Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,19 +5012,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>TALON</v>
+        <v>Flash</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>998.9942413303544</v>
+        <v>985</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-09-06T03:52:19.722Z</v>
+        <v>2026-07-30T05:44:09.112Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,19 +5065,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Into the Beach</v>
+        <v>ESC</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>996.0904918173039</v>
+        <v>985</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J89" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K89" t="str">
         <v>none</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-07-23T22:12:51.919Z</v>
+        <v>2026-07-30T05:43:58.246Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,19 +5118,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mythic</v>
+        <v>00 Nation</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>986.2948766874508</v>
+        <v>985</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J90" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K90" t="str">
         <v>none</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-07-23T22:00:15.992Z</v>
+        <v>2026-07-30T05:43:50.812Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,19 +5171,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MOUZ</v>
+        <v>Quantum Bellator Fire</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91">
-        <v>985.5794629886747</v>
+        <v>985</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J91" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K91" t="str">
         <v>none</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-09-06T03:52:26.404Z</v>
+        <v>2026-07-30T05:43:19.675Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>GhoulsW</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-07-30T05:44:28.360Z</v>
+        <v>2026-07-30T05:43:07.819Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,7 +5277,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HAVU</v>
+        <v>Nordix</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-07-30T05:44:22.588Z</v>
+        <v>2026-07-30T05:42:58.796Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-07-30T05:44:15.749Z</v>
+        <v>2026-07-30T05:42:49.775Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Flash</v>
+        <v>QMISTRY</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-07-30T05:44:09.112Z</v>
+        <v>2026-07-30T05:42:44.510Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ESC</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-07-30T05:43:58.246Z</v>
+        <v>2026-07-30T05:42:06.941Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>00 Nation</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-07-30T05:43:50.812Z</v>
+        <v>2026-07-30T05:41:55.808Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Quantum Bellator Fire</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J98" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K98" t="str">
         <v>none</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-07-30T05:43:19.675Z</v>
+        <v>2026-07-30T05:41:42.732Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Astralis Talent</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-07-30T05:43:07.819Z</v>
+        <v>2026-07-30T05:39:19.440Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nordix</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-07-30T05:42:58.796Z</v>
+        <v>2026-07-30T05:39:12.741Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>NOVAQ</v>
+        <v>ad hoc</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-07-30T05:42:49.775Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>QMISTRY</v>
+        <v>SAW</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-07-30T05:42:44.510Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>MOUZ NXT</v>
+        <v>NomadS</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J103" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K103" t="str">
         <v>none</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-07-30T05:42:06.941Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>FlyQuest RED</v>
+        <v>Outsiders</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-07-30T05:41:55.808Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>100 Thieves</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J105" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K105" t="str">
         <v>none</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-07-30T05:41:42.732Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>NIP Impact</v>
+        <v>The Dice</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5993,7 +5993,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J106" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K106" t="str">
         <v>none</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-07-30T05:39:19.440Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Heroic Academy</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6046,7 +6046,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J107" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K107" t="str">
         <v>none</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-07-30T05:39:12.741Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ad hoc</v>
+        <v>ODDIK</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6099,7 +6099,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J108" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K108" t="str">
         <v>none</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SAW</v>
+        <v>inSanitY</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>NomadS</v>
+        <v>Sangal</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6205,7 +6205,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J110" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K110" t="str">
         <v>none</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Outsiders</v>
+        <v>9Pandas</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J111" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K111" t="str">
         <v>none</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Red Viperz</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>The Dice</v>
+        <v>CatEvil</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J113" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K113" t="str">
         <v>none</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Victores Sumus</v>
+        <v>Carnival</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ODDIK</v>
+        <v>Vantage</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6470,7 +6470,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J115" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K115" t="str">
         <v>none</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>inSanitY</v>
+        <v>Skinvault</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J116" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K116" t="str">
         <v>none</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sangal</v>
+        <v>Wings Up</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6576,7 +6576,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J117" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K117" t="str">
         <v>none</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>9Pandas</v>
+        <v>Venom</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J118" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K118" t="str">
         <v>none</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gods Reign</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>CatEvil</v>
+        <v>Galorys</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J120" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K120" t="str">
         <v>none</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Carnival</v>
+        <v>devils.one</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Vantage</v>
+        <v>Sharks</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J122" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K122" t="str">
         <v>none</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Skinvault</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Wings Up</v>
+        <v>Complexity</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J124" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K124" t="str">
         <v>none</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Venom</v>
+        <v>Case</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7000,7 +7000,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J125" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K125" t="str">
         <v>none</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GamerLegion</v>
+        <v>KRU</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Galorys</v>
+        <v>paiN</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>devils.one</v>
+        <v>Vexed</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,19 +7185,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Sharks</v>
+        <v>ARCRED</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-09-08T12:45:52.294Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,19 +7238,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Kappa Bar</v>
+        <v>Dignitas</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,19 +7291,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Complexity</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,19 +7344,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Case</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,19 +7397,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>KRU</v>
+        <v>ShindeN</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,19 +7450,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>paiN</v>
+        <v>Wildcard</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J134" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K134" t="str">
         <v>none</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,19 +7503,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Vexed</v>
+        <v>SK</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,19 +7556,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Aurora</v>
+        <v>3DMAX</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>2</v>
       </c>
       <c r="E136">
-        <v>984.9739063475313</v>
+        <v>984.6909026700279</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-09-06T03:52:33.086Z</v>
+        <v>2026-09-08T12:44:53.425Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,19 +7609,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Dignitas</v>
+        <v>Underground</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137">
-        <v>984.7039370196626</v>
+        <v>984.4331277144938</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-09-08T12:44:38.294Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,19 +7662,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>VP.Prodigy</v>
+        <v>Aravt</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E138">
-        <v>984.7039370196626</v>
+        <v>984.42090838896</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-09-08T12:45:59.510Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,19 +7715,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Virtus.pro</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E139">
-        <v>984.7039370196626</v>
+        <v>984.42090838896</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J139" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K139" t="str">
         <v>none</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-09-08T12:45:02.441Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ShindeN</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7780,7 +7780,7 @@
         <v>2</v>
       </c>
       <c r="E140">
-        <v>984.7039370196626</v>
+        <v>984.0694284244669</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-09-08T12:44:45.656Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,19 +7821,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Wildcard</v>
+        <v>TALON</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E141">
-        <v>984.7039370196626</v>
+        <v>983.7424573635163</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-09-08T12:45:14.013Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,19 +7874,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SK</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E142">
-        <v>984.7039370196626</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7901,7 +7901,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J142" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K142" t="str">
         <v>none</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,19 +7927,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>NAVI Junior</v>
+        <v>Legacy</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E143">
-        <v>983.2698348870488</v>
+        <v>976.9354856610739</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7954,7 +7954,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J143" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K143" t="str">
         <v>none</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-07-23T22:02:02.134Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,19 +7980,19 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Legacy</v>
+        <v>9z</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E144">
-        <v>976.9354856610739</v>
+        <v>971.3809496889581</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-07-23T22:02:02.134Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>9z</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8045,7 +8045,7 @@
         <v>3</v>
       </c>
       <c r="E145">
-        <v>971.3809496889581</v>
+        <v>971.0310326935038</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-07-23T22:01:33.382Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>paiN Academy</v>
+        <v>Aurora</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8098,7 +8098,7 @@
         <v>3</v>
       </c>
       <c r="E146">
-        <v>971.0310326935038</v>
+        <v>970.9387896370487</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -8113,7 +8113,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J146" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K146" t="str">
         <v>none</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-07-23T22:01:33.382Z</v>
+        <v>2026-09-08T12:46:09.197Z</v>
       </c>
       <c r="N146" t="str">
         <v/>

--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -825,19 +825,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Natus Vincere</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1064.5550904053082</v>
+        <v>1072.8968031763707</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -846,22 +846,22 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>Tier 3</v>
       </c>
       <c r="J9" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K9" t="str">
-        <v>none</v>
+        <v>global</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-06-26T13:18:10.268Z</v>
+        <v>2026-09-18T03:05:55.555Z</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -878,19 +878,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Liquid</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>1064.3973274912723</v>
+        <v>1064.5550904053082</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J10" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K10" t="str">
         <v>none</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-06-26T13:20:06.028Z</v>
+        <v>2026-06-26T13:18:10.268Z</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -931,19 +931,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Elevate</v>
+        <v>Liquid</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>1056.7441503790217</v>
+        <v>1064.3973274912723</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J11" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K11" t="str">
         <v>none</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-05-30T04:01:58.103Z</v>
+        <v>2026-06-26T13:20:06.028Z</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -984,7 +984,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Eternal Fire</v>
+        <v>Elevate</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -996,7 +996,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>1055.7875002516132</v>
+        <v>1056.7441503790217</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J12" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K12" t="str">
         <v>none</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-30T04:01:51.528Z</v>
+        <v>2026-05-30T04:01:58.103Z</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1037,19 +1037,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FURIA</v>
+        <v>Eternal Fire</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>1050.7178542874221</v>
+        <v>1055.7875002516132</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="str">
         <v>Tier 3</v>
       </c>
       <c r="J13" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K13" t="str">
-        <v>regional</v>
+        <v>none</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-07-23T22:29:09.347Z</v>
+        <v>2026-05-30T04:01:51.528Z</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1090,19 +1090,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Titan</v>
+        <v>FURIA</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>1046.4273525065098</v>
+        <v>1050.7178542874221</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>Tier 3</v>
@@ -1120,13 +1120,13 @@
         <v>AM</v>
       </c>
       <c r="K14" t="str">
-        <v>none</v>
+        <v>regional</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-05-30T04:00:20.081Z</v>
+        <v>2026-07-23T22:29:09.347Z</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Vox Eminor</v>
+        <v>Titan</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>1045.6755056188154</v>
+        <v>1046.4273525065098</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J15" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K15" t="str">
         <v>none</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-08-23T07:39:22.255Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1196,19 +1196,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Astana Dragons</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1045.0604120732232</v>
+        <v>1045.6755056188154</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-08-23T07:39:14.984Z</v>
+        <v>2026-08-23T07:39:22.255Z</v>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -1249,19 +1249,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1041.3191963490904</v>
+        <v>1045.0604120732232</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J17" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K17" t="str">
         <v>none</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-07-23T22:16:25.593Z</v>
+        <v>2026-08-23T07:39:14.984Z</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -1302,19 +1302,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Verdant</v>
+        <v>AMKAL</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>1038.7190184710753</v>
+        <v>1041.3191963490904</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J18" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K18" t="str">
         <v>none</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-02-28T06:29:24.671Z</v>
+        <v>2026-07-23T22:16:25.593Z</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1355,19 +1355,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>PARIVISION</v>
+        <v>Verdant</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>1034.630067328374</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-05-01T06:07:06.437Z</v>
+        <v>2026-02-28T06:29:24.671Z</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cloud9</v>
+        <v>PARIVISION</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>1031.0582679094105</v>
+        <v>1034.630067328374</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-05-01T06:06:54.331Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Heroic</v>
+        <v>Imperial</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1030.413991476608</v>
+        <v>1031.1553290853929</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J21" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K21" t="str">
         <v>none</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-05-01T06:08:21.905Z</v>
+        <v>2026-09-18T03:05:26.098Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Entropiq</v>
+        <v>Cloud9</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>1029.3999079514006</v>
+        <v>1031.0582679094105</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J22" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K22" t="str">
         <v>none</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-07-23T22:14:26.816Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Lux Tenebris</v>
+        <v>Heroic</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>1027.7153682632659</v>
+        <v>1030.413991476608</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-09-08T12:46:09.197Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bounty Hunters</v>
+        <v>BC.Game</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>1017.2412711985547</v>
+        <v>1030.0316475527723</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-09-18T03:05:16.918Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Spirit</v>
+        <v>Entropiq</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25">
-        <v>1016.7402640066111</v>
+        <v>1029.3999079514006</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J25" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K25" t="str">
         <v>none</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lynn Vision</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>1015.2960629803374</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-09-08T12:45:52.294Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Enemy</v>
+        <v>Spirit</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>1015.2835913684207</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J27" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K27" t="str">
         <v>none</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-09-08T12:44:38.294Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Envy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>2</v>
       </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
       <c r="E28">
-        <v>1015.2830286307026</v>
+        <v>1015.0604120732232</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-09-08T12:45:02.441Z</v>
+        <v>2026-08-23T07:39:14.984Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Imperial</v>
+        <v>The Huns</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>1015.2830286307026</v>
+        <v>1015</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-09-08T12:45:59.510Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BC.Game</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>1015.251783966838</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-09-08T12:45:14.013Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>1015.0604120732232</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-23T07:39:14.984Z</v>
+        <v>2026-08-23T07:38:19.410Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Astralis</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>1015.0130343496347</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-09-08T12:44:53.425Z</v>
+        <v>2026-08-23T07:38:11.231Z</v>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Huns</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>1015</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J33" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K33" t="str">
         <v>none</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-08-23T07:38:02.605Z</v>
       </c>
       <c r="N33" t="str">
         <v/>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Onyx Ravens</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>1014.9877256835035</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J34" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K34" t="str">
         <v>none</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-08-23T07:37:55.979Z</v>
       </c>
       <c r="N34" t="str">
         <v/>
@@ -2203,19 +2203,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Wildcard Academy</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1014.7261395369545</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-08-23T07:38:19.410Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N35" t="str">
         <v/>
@@ -2256,19 +2256,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BIG Academy</v>
+        <v>TYLOO</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>1014.7261395369545</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J36" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K36" t="str">
         <v>none</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-08-23T07:38:11.231Z</v>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N36" t="str">
         <v/>
@@ -2309,19 +2309,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SKYFURY</v>
+        <v>OG</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>1014.7261395369545</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-08-23T07:38:02.605Z</v>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N37" t="str">
         <v/>
@@ -2362,19 +2362,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENCE Academy</v>
+        <v>BESTIA</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>1014.7261395369545</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J38" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K38" t="str">
         <v>none</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-08-23T07:37:55.979Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N38" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Counter Logic</v>
+        <v>G2</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>1014.6510123894305</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-07-07T04:08:50.601Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N39" t="str">
         <v/>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TYLOO</v>
+        <v>hoorai</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>1014.128742285643</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J40" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K40" t="str">
         <v>none</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N40" t="str">
         <v/>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>OG</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -2530,10 +2530,10 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>1013.5266895185538</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J41" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K41" t="str">
         <v>none</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N41" t="str">
         <v/>
@@ -2574,19 +2574,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>BESTIA</v>
+        <v>Astralis</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>1005.0046329623956</v>
+        <v>1000.301098393133</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J42" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K42" t="str">
         <v>none</v>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-09-18T03:05:16.918Z</v>
       </c>
       <c r="N42" t="str">
         <v/>
@@ -2627,19 +2627,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>G2</v>
+        <v>Avangar</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>1002.6421965170028</v>
+        <v>1000</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J43" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K43" t="str">
         <v>none</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v/>
       </c>
       <c r="N43" t="str">
         <v/>
@@ -2680,19 +2680,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MOUZ</v>
+        <v>Bravado</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>1001.5100345642078</v>
+        <v>1000</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J44" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K44" t="str">
         <v>none</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-09-08T12:44:45.656Z</v>
+        <v/>
       </c>
       <c r="N44" t="str">
         <v/>
@@ -2733,19 +2733,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>hoorai</v>
+        <v>FORZE</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>1000.4888979238718</v>
+        <v>1000</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v/>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -2786,19 +2786,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Take Flyte</v>
+        <v>GATERON</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>1000.3086743488057</v>
+        <v>1000</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-07-23T22:14:26.816Z</v>
+        <v/>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Avangar</v>
+        <v>Hesta</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J47" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K47" t="str">
         <v>none</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bravado</v>
+        <v>kONO</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>FORZE</v>
+        <v>LGB</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Hesta</v>
+        <v>Shika</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J51" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K51" t="str">
         <v>none</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>kONO</v>
+        <v>Tsunami</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,19 +3157,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>LGB</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N53" t="str">
         <v/>
@@ -3210,19 +3210,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rogue</v>
+        <v>True Rippers</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N54" t="str">
         <v/>
@@ -3263,19 +3263,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Shika</v>
+        <v>FaZe</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J55" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K55" t="str">
         <v>none</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N55" t="str">
         <v/>
@@ -3316,19 +3316,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tsunami</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N56" t="str">
         <v/>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Spirit Academy</v>
+        <v>GODSENT</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -3396,7 +3396,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J57" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K57" t="str">
         <v>none</v>
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N57" t="str">
         <v/>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>True Rippers</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -3434,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>999.7251809772306</v>
+        <v>999.7134559394154</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J58" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K58" t="str">
         <v>none</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-09-18T03:04:37.198Z</v>
       </c>
       <c r="N58" t="str">
         <v/>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>FaZe</v>
+        <v>Envy</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -3487,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="E59">
-        <v>999.7251809772306</v>
+        <v>999.7131051873197</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-09-18T03:04:43.340Z</v>
       </c>
       <c r="N59" t="str">
         <v/>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>iBUYPOWER</v>
+        <v>Enemy</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -3540,7 +3540,7 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>999.7251809772306</v>
+        <v>999.7122425131721</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-09-18T03:04:48.530Z</v>
       </c>
       <c r="N60" t="str">
         <v/>
@@ -3581,19 +3581,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>GODSENT</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>999.7251809772306</v>
+        <v>999.7039370196626</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J61" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K61" t="str">
         <v>none</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-08-08T06:10:52.072Z</v>
       </c>
       <c r="N61" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>MAD Lions</v>
+        <v>Kinguin</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -3661,7 +3661,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J62" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K62" t="str">
         <v>none</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="str">
-        <v>2026-08-08T06:10:52.072Z</v>
+        <v>2026-08-08T06:06:19.166Z</v>
       </c>
       <c r="N62" t="str">
         <v/>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Kinguin</v>
+        <v>Gambit</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -3714,7 +3714,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J63" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K63" t="str">
         <v>none</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="str">
-        <v>2026-08-08T06:06:19.166Z</v>
+        <v>2026-08-08T06:06:03.563Z</v>
       </c>
       <c r="N63" t="str">
         <v/>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gambit</v>
+        <v>VeryGames</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -3767,7 +3767,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J64" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K64" t="str">
         <v>none</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="str">
-        <v>2026-08-08T06:06:03.563Z</v>
+        <v>2026-08-08T06:05:55.763Z</v>
       </c>
       <c r="N64" t="str">
         <v/>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>VeryGames</v>
+        <v>Misfits</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -3820,7 +3820,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J65" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K65" t="str">
         <v>none</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="str">
-        <v>2026-08-08T06:05:55.763Z</v>
+        <v>2026-08-08T06:04:44.394Z</v>
       </c>
       <c r="N65" t="str">
         <v/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Misfits</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -3873,7 +3873,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J66" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K66" t="str">
         <v>none</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="str">
-        <v>2026-08-08T06:04:44.394Z</v>
+        <v>2026-08-08T06:04:29.697Z</v>
       </c>
       <c r="N66" t="str">
         <v/>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Space Soldiers</v>
+        <v>mousesports</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="str">
-        <v>2026-08-08T06:04:29.697Z</v>
+        <v>2026-08-08T06:04:14.871Z</v>
       </c>
       <c r="N67" t="str">
         <v/>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>mousesports</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="str">
-        <v>2026-08-08T06:04:14.871Z</v>
+        <v>2026-08-08T06:03:54.346Z</v>
       </c>
       <c r="N68" t="str">
         <v/>
@@ -4005,19 +4005,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Movistar KOI</v>
+        <v>M80</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>999.7039370196626</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4032,7 +4032,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J69" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K69" t="str">
         <v>none</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="str">
-        <v>2026-08-08T06:03:54.346Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N69" t="str">
         <v/>
@@ -4058,19 +4058,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>M80</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>999.672340544519</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J70" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K70" t="str">
         <v>none</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N70" t="str">
         <v/>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Orbit</v>
       </c>
       <c r="B71">
         <v>3</v>
@@ -4123,7 +4123,7 @@
         <v>3</v>
       </c>
       <c r="E71">
-        <v>999.4408194717619</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J71" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K71" t="str">
         <v>none</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N71" t="str">
         <v/>
@@ -4164,19 +4164,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Orbit</v>
+        <v>Alliance</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N72" t="str">
         <v/>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Alliance</v>
+        <v>Homyno</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -4244,7 +4244,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J73" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K73" t="str">
         <v>none</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N73" t="str">
         <v/>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Homyno</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -4297,7 +4297,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J74" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K74" t="str">
         <v>none</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>MenaceGG</v>
+        <v>Solid</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N75" t="str">
         <v/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Solid</v>
+        <v>ENCE</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ENCE</v>
+        <v>Nexus</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nexus</v>
+        <v>MIBR</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4509,7 +4509,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J78" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K78" t="str">
         <v>none</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>MIBR</v>
+        <v>Wizards</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4547,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,19 +4588,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Wizards</v>
+        <v>RED Canids</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>999.4062521695108</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>RED Canids</v>
+        <v>Rebels</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E81">
-        <v>999.3397745397444</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J81" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K81" t="str">
         <v>none</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Rebels</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>999.3232682842747</v>
+        <v>996.0904918173039</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J82" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K82" t="str">
         <v>none</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-23T22:12:51.919Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Into the Beach</v>
+        <v>MOUZ</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>996.0904918173039</v>
+        <v>987.1122509065335</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-07-23T22:12:51.919Z</v>
+        <v>2026-09-18T03:04:26.253Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
